--- a/docs/harness/wirelist/ECU-engine-wirelist.xlsx
+++ b/docs/harness/wirelist/ECU-engine-wirelist.xlsx
@@ -764,7 +764,7 @@
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="36" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
     <col width="32" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -12875,12 +12875,12 @@
       <c r="P118" s="45" t="inlineStr"/>
       <c r="Q118" s="46" t="inlineStr">
         <is>
-          <t>STUD.M6-ECU</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="R118" s="47" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
+          <t>Chassis GND (POWER box NEG bar M8 stud (glove box))</t>
         </is>
       </c>
       <c r="S118" s="48" t="inlineStr">
@@ -13670,12 +13670,12 @@
       <c r="P125" s="29" t="inlineStr"/>
       <c r="Q125" s="30" t="inlineStr">
         <is>
-          <t>STUD.M6-ECU</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="R125" s="31" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
+          <t>Chassis GND (POWER box NEG bar M8 stud (glove box))</t>
         </is>
       </c>
       <c r="S125" s="32" t="inlineStr">
@@ -14465,7 +14465,7 @@
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
@@ -15178,12 +15178,12 @@
       </c>
       <c r="D13" s="30" t="inlineStr">
         <is>
-          <t>STUD.M6-ECU</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="E13" s="31" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
+          <t>Chassis GND (POWER box NEG bar M8 stud (glove box))</t>
         </is>
       </c>
       <c r="F13" s="32" t="n">
@@ -19056,7 +19056,7 @@
       </c>
       <c r="I63" s="59" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
+          <t>Chassis GND (POWER box NEG bar M8 stud (glove box))</t>
         </is>
       </c>
       <c r="J63" s="60" t="inlineStr">
